--- a/results/05_modeling_nested/ALL_summary.xlsx
+++ b/results/05_modeling_nested/ALL_summary.xlsx
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -539,10 +539,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7416451769600094</v>
+        <v>0.7371297104138026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01993688661995984</v>
+        <v>0.02055176014088759</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1154322800342247</v>
+        <v>0.113979645704231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01432159611287153</v>
+        <v>0.01327209032282319</v>
       </c>
     </row>
     <row r="3">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.778291616922111</v>
+        <v>0.7638655851081998</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02016460778089968</v>
+        <v>0.01830461526364529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1366611393084907</v>
+        <v>0.1305084174604524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01644375607216518</v>
+        <v>0.01322728173796852</v>
       </c>
     </row>
   </sheetData>
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.740204074741885</v>
+        <v>0.7423180768872754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01632377788364275</v>
+        <v>0.01740707860779314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1504672166943709</v>
+        <v>0.150418939148557</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01174477485781384</v>
+        <v>0.01096860461154251</v>
       </c>
     </row>
     <row r="3">
@@ -849,16 +849,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8124041670509727</v>
+        <v>0.8102974592286788</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00960631081931577</v>
+        <v>0.008404306776686604</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2179801169523388</v>
+        <v>0.2163882894451978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01386992304711891</v>
+        <v>0.01225359127876926</v>
       </c>
     </row>
   </sheetData>
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8380082807867801</v>
+        <v>0.8384060741259433</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02096671842468235</v>
+        <v>0.02144293790929938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3626783404222963</v>
+        <v>0.3621556760174849</v>
       </c>
       <c r="E2" t="n">
-        <v>0.036706105017073</v>
+        <v>0.03892340905464424</v>
       </c>
     </row>
     <row r="3">
@@ -928,16 +928,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8635755888181507</v>
+        <v>0.8665735005647537</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007267449988741658</v>
+        <v>0.008279770287604037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4197146136049616</v>
+        <v>0.4183159022170709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05043702845977172</v>
+        <v>0.05664601097712555</v>
       </c>
     </row>
   </sheetData>
